--- a/inst/grading_rulesets.xlsx
+++ b/inst/grading_rulesets.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="126">
   <si>
     <t xml:space="preserve">GRADING_RULESET</t>
   </si>
@@ -290,6 +290,24 @@
   </si>
   <si>
     <t xml:space="preserve">Percentage of observational units with a total response time outside the expected interval (admissible values) provided in the metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCT_ssc_sumattit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of observational units with incorrect responses to attention check items outside the expected interval provided in the metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCT_ssc_psychom_ant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of observational units with a psychometric antonyms value outside the expected interval (admissible values) provided in the metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCT_ssc_psychom_syn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of observational units with a psychometric synonyms value outside the expected interval (admissible values) provided in the metadata</t>
   </si>
   <si>
     <t xml:space="preserve">CLS_int_vfe_type</t>
@@ -502,37 +520,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -671,8 +689,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.44"/>
@@ -1352,43 +1370,81 @@
       <c r="A31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="D31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="4" t="s">
         <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>93</v>
       </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>95</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1399,7 +1455,7 @@
       <c r="B35" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1495,10 +1551,10 @@
       <c r="A44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1506,14 +1562,46 @@
       <c r="A45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
